--- a/H5509_V2/bin/Debug/H5509_alarm.xlsx
+++ b/H5509_V2/bin/Debug/H5509_alarm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\H5509_V2\H5509_V2\bin\Debug\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E41F5151-AB75-45CB-B84C-078C98F43A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DFE2497-3FFD-4A16-B48B-DDFC76D09329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="3690" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4965" yWindow="750" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4572" uniqueCount="2804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4584" uniqueCount="2808">
   <si>
     <t>C_EmptySidePush--Cylinder On Sensor Can not Detect On</t>
   </si>
@@ -7698,9 +7698,6 @@
   </si>
   <si>
     <t>System Error--Not Key In Data:</t>
-  </si>
-  <si>
-    <t>系统错误--没有输入数据</t>
   </si>
   <si>
     <t>System Error--Lot No: key in error</t>
@@ -8474,6 +8471,22 @@
   </si>
   <si>
     <t>请打开Load仓门等待下降至底部，关上仓门后再按开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Empty区后感应器到Tray盘放歪</t>
+  </si>
+  <si>
+    <t>Load区后感应器到Tray盘放歪</t>
+  </si>
+  <si>
+    <t>Auto1区后感应器到Tray盘放歪</t>
+  </si>
+  <si>
+    <t>Auto2区后感应器到Tray盘放歪</t>
+  </si>
+  <si>
+    <t>测试机tester接收的通讯数据(Data)解析失败！详细信息：Msg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8481,7 +8494,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8504,6 +8517,12 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -8525,7 +8544,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8539,6 +8558,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -8814,7 +8837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1524"/>
+  <dimension ref="A1:E1528"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5" style="1" customWidth="1"/>
@@ -9140,7 +9163,7 @@
         <v>1009000</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>37</v>
@@ -13172,7 +13195,7 @@
         <v>509</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>228</v>
@@ -13801,7 +13824,7 @@
         <v>548</v>
       </c>
       <c r="D293" s="6" t="s">
-        <v>2670</v>
+        <v>2669</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>257</v>
@@ -13835,7 +13858,7 @@
         <v>551</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>2671</v>
+        <v>2670</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>257</v>
@@ -20975,7 +20998,7 @@
         <v>1116</v>
       </c>
       <c r="D715" s="2" t="s">
-        <v>2673</v>
+        <v>2672</v>
       </c>
       <c r="E715" s="1" t="s">
         <v>1118</v>
@@ -20992,7 +21015,7 @@
         <v>1119</v>
       </c>
       <c r="D716" s="2" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="E716" s="1" t="s">
         <v>1118</v>
@@ -21009,7 +21032,7 @@
         <v>1121</v>
       </c>
       <c r="D717" s="2" t="s">
-        <v>2675</v>
+        <v>2674</v>
       </c>
       <c r="E717" s="1" t="s">
         <v>1118</v>
@@ -21026,7 +21049,7 @@
         <v>1123</v>
       </c>
       <c r="D718" s="2" t="s">
-        <v>2676</v>
+        <v>2675</v>
       </c>
       <c r="E718" s="1" t="s">
         <v>1118</v>
@@ -21043,7 +21066,7 @@
         <v>1125</v>
       </c>
       <c r="D719" s="2" t="s">
-        <v>2677</v>
+        <v>2676</v>
       </c>
       <c r="E719" s="1" t="s">
         <v>1118</v>
@@ -21060,7 +21083,7 @@
         <v>1127</v>
       </c>
       <c r="D720" s="2" t="s">
-        <v>2678</v>
+        <v>2677</v>
       </c>
       <c r="E720" s="1" t="s">
         <v>1118</v>
@@ -21077,7 +21100,7 @@
         <v>1129</v>
       </c>
       <c r="D721" s="2" t="s">
-        <v>2679</v>
+        <v>2678</v>
       </c>
       <c r="E721" s="1" t="s">
         <v>1118</v>
@@ -21094,7 +21117,7 @@
         <v>1131</v>
       </c>
       <c r="D722" s="2" t="s">
-        <v>2680</v>
+        <v>2679</v>
       </c>
       <c r="E722" s="1" t="s">
         <v>1118</v>
@@ -21111,7 +21134,7 @@
         <v>1133</v>
       </c>
       <c r="D723" s="2" t="s">
-        <v>2681</v>
+        <v>2680</v>
       </c>
       <c r="E723" s="1" t="s">
         <v>1118</v>
@@ -21128,7 +21151,7 @@
         <v>1135</v>
       </c>
       <c r="D724" s="2" t="s">
-        <v>2682</v>
+        <v>2681</v>
       </c>
       <c r="E724" s="1" t="s">
         <v>1118</v>
@@ -21145,7 +21168,7 @@
         <v>1137</v>
       </c>
       <c r="D725" s="2" t="s">
-        <v>2683</v>
+        <v>2682</v>
       </c>
       <c r="E725" s="1" t="s">
         <v>1118</v>
@@ -21162,7 +21185,7 @@
         <v>1139</v>
       </c>
       <c r="D726" s="2" t="s">
-        <v>2684</v>
+        <v>2683</v>
       </c>
       <c r="E726" s="1" t="s">
         <v>1118</v>
@@ -21179,7 +21202,7 @@
         <v>1141</v>
       </c>
       <c r="D727" s="2" t="s">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="E727" s="1" t="s">
         <v>1118</v>
@@ -21196,7 +21219,7 @@
         <v>1143</v>
       </c>
       <c r="D728" s="2" t="s">
-        <v>2686</v>
+        <v>2685</v>
       </c>
       <c r="E728" s="1" t="s">
         <v>1118</v>
@@ -21213,7 +21236,7 @@
         <v>1145</v>
       </c>
       <c r="D729" s="2" t="s">
-        <v>2687</v>
+        <v>2686</v>
       </c>
       <c r="E729" s="1" t="s">
         <v>1118</v>
@@ -21230,7 +21253,7 @@
         <v>1147</v>
       </c>
       <c r="D730" s="2" t="s">
-        <v>2688</v>
+        <v>2687</v>
       </c>
       <c r="E730" s="1" t="s">
         <v>1118</v>
@@ -21247,7 +21270,7 @@
         <v>1149</v>
       </c>
       <c r="D731" s="2" t="s">
-        <v>2689</v>
+        <v>2688</v>
       </c>
       <c r="E731" s="1" t="s">
         <v>1118</v>
@@ -21264,7 +21287,7 @@
         <v>1151</v>
       </c>
       <c r="D732" s="2" t="s">
-        <v>2690</v>
+        <v>2689</v>
       </c>
       <c r="E732" s="1" t="s">
         <v>1118</v>
@@ -21281,7 +21304,7 @@
         <v>1153</v>
       </c>
       <c r="D733" s="2" t="s">
-        <v>2691</v>
+        <v>2690</v>
       </c>
       <c r="E733" s="1" t="s">
         <v>1118</v>
@@ -21298,7 +21321,7 @@
         <v>1155</v>
       </c>
       <c r="D734" s="2" t="s">
-        <v>2692</v>
+        <v>2691</v>
       </c>
       <c r="E734" s="1" t="s">
         <v>1118</v>
@@ -21315,7 +21338,7 @@
         <v>1157</v>
       </c>
       <c r="D735" s="2" t="s">
-        <v>2693</v>
+        <v>2692</v>
       </c>
       <c r="E735" s="1" t="s">
         <v>1118</v>
@@ -21332,7 +21355,7 @@
         <v>1159</v>
       </c>
       <c r="D736" s="2" t="s">
-        <v>2694</v>
+        <v>2693</v>
       </c>
       <c r="E736" s="1" t="s">
         <v>1118</v>
@@ -21349,7 +21372,7 @@
         <v>1161</v>
       </c>
       <c r="D737" s="2" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
       <c r="E737" s="1" t="s">
         <v>1118</v>
@@ -21366,7 +21389,7 @@
         <v>1163</v>
       </c>
       <c r="D738" s="2" t="s">
-        <v>2696</v>
+        <v>2695</v>
       </c>
       <c r="E738" s="1" t="s">
         <v>1118</v>
@@ -21383,7 +21406,7 @@
         <v>1165</v>
       </c>
       <c r="D739" s="2" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E739" s="1" t="s">
         <v>1118</v>
@@ -21400,7 +21423,7 @@
         <v>1167</v>
       </c>
       <c r="D740" s="2" t="s">
-        <v>2698</v>
+        <v>2697</v>
       </c>
       <c r="E740" s="1" t="s">
         <v>1118</v>
@@ -21417,7 +21440,7 @@
         <v>1169</v>
       </c>
       <c r="D741" s="2" t="s">
-        <v>2699</v>
+        <v>2698</v>
       </c>
       <c r="E741" s="1" t="s">
         <v>1118</v>
@@ -21434,7 +21457,7 @@
         <v>1171</v>
       </c>
       <c r="D742" s="2" t="s">
-        <v>2700</v>
+        <v>2699</v>
       </c>
       <c r="E742" s="1" t="s">
         <v>1118</v>
@@ -21451,7 +21474,7 @@
         <v>1173</v>
       </c>
       <c r="D743" s="2" t="s">
-        <v>2701</v>
+        <v>2700</v>
       </c>
       <c r="E743" s="1" t="s">
         <v>1118</v>
@@ -21468,7 +21491,7 @@
         <v>1175</v>
       </c>
       <c r="D744" s="2" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
       <c r="E744" s="1" t="s">
         <v>1118</v>
@@ -21485,7 +21508,7 @@
         <v>1177</v>
       </c>
       <c r="D745" s="2" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
       <c r="E745" s="1" t="s">
         <v>1118</v>
@@ -21502,7 +21525,7 @@
         <v>1179</v>
       </c>
       <c r="D746" s="2" t="s">
-        <v>2704</v>
+        <v>2703</v>
       </c>
       <c r="E746" s="1" t="s">
         <v>1118</v>
@@ -21519,7 +21542,7 @@
         <v>1181</v>
       </c>
       <c r="D747" s="2" t="s">
-        <v>2705</v>
+        <v>2704</v>
       </c>
       <c r="E747" s="1" t="s">
         <v>1118</v>
@@ -21536,7 +21559,7 @@
         <v>1183</v>
       </c>
       <c r="D748" s="2" t="s">
-        <v>2706</v>
+        <v>2705</v>
       </c>
       <c r="E748" s="1" t="s">
         <v>1118</v>
@@ -21553,7 +21576,7 @@
         <v>1185</v>
       </c>
       <c r="D749" s="2" t="s">
-        <v>2707</v>
+        <v>2706</v>
       </c>
       <c r="E749" s="1" t="s">
         <v>1118</v>
@@ -21570,7 +21593,7 @@
         <v>1187</v>
       </c>
       <c r="D750" s="2" t="s">
-        <v>2708</v>
+        <v>2707</v>
       </c>
       <c r="E750" s="1" t="s">
         <v>1118</v>
@@ -21587,7 +21610,7 @@
         <v>1189</v>
       </c>
       <c r="D751" s="2" t="s">
-        <v>2709</v>
+        <v>2708</v>
       </c>
       <c r="E751" s="1" t="s">
         <v>1118</v>
@@ -21604,7 +21627,7 @@
         <v>1191</v>
       </c>
       <c r="D752" s="2" t="s">
-        <v>2710</v>
+        <v>2709</v>
       </c>
       <c r="E752" s="1" t="s">
         <v>1118</v>
@@ -21621,7 +21644,7 @@
         <v>1193</v>
       </c>
       <c r="D753" s="2" t="s">
-        <v>2711</v>
+        <v>2710</v>
       </c>
       <c r="E753" s="1" t="s">
         <v>1118</v>
@@ -21638,7 +21661,7 @@
         <v>1195</v>
       </c>
       <c r="D754" s="2" t="s">
-        <v>2712</v>
+        <v>2711</v>
       </c>
       <c r="E754" s="1" t="s">
         <v>1118</v>
@@ -21655,7 +21678,7 @@
         <v>1197</v>
       </c>
       <c r="D755" s="2" t="s">
-        <v>2713</v>
+        <v>2712</v>
       </c>
       <c r="E755" s="1" t="s">
         <v>1118</v>
@@ -21672,7 +21695,7 @@
         <v>1199</v>
       </c>
       <c r="D756" s="2" t="s">
-        <v>2714</v>
+        <v>2713</v>
       </c>
       <c r="E756" s="1" t="s">
         <v>1118</v>
@@ -21689,7 +21712,7 @@
         <v>1201</v>
       </c>
       <c r="D757" s="2" t="s">
-        <v>2715</v>
+        <v>2714</v>
       </c>
       <c r="E757" s="1" t="s">
         <v>1118</v>
@@ -21706,7 +21729,7 @@
         <v>1203</v>
       </c>
       <c r="D758" s="2" t="s">
-        <v>2716</v>
+        <v>2715</v>
       </c>
       <c r="E758" s="1" t="s">
         <v>1118</v>
@@ -21723,7 +21746,7 @@
         <v>1205</v>
       </c>
       <c r="D759" s="2" t="s">
-        <v>2717</v>
+        <v>2716</v>
       </c>
       <c r="E759" s="1" t="s">
         <v>1118</v>
@@ -21740,7 +21763,7 @@
         <v>1207</v>
       </c>
       <c r="D760" s="2" t="s">
-        <v>2718</v>
+        <v>2717</v>
       </c>
       <c r="E760" s="1" t="s">
         <v>1118</v>
@@ -21757,7 +21780,7 @@
         <v>1209</v>
       </c>
       <c r="D761" s="2" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
       <c r="E761" s="1" t="s">
         <v>1118</v>
@@ -21774,7 +21797,7 @@
         <v>1211</v>
       </c>
       <c r="D762" s="2" t="s">
-        <v>2720</v>
+        <v>2719</v>
       </c>
       <c r="E762" s="1" t="s">
         <v>1118</v>
@@ -21791,7 +21814,7 @@
         <v>1213</v>
       </c>
       <c r="D763" s="2" t="s">
-        <v>2721</v>
+        <v>2720</v>
       </c>
       <c r="E763" s="1" t="s">
         <v>1118</v>
@@ -21808,7 +21831,7 @@
         <v>1215</v>
       </c>
       <c r="D764" s="2" t="s">
-        <v>2722</v>
+        <v>2721</v>
       </c>
       <c r="E764" s="1" t="s">
         <v>1118</v>
@@ -21825,7 +21848,7 @@
         <v>1217</v>
       </c>
       <c r="D765" s="2" t="s">
-        <v>2723</v>
+        <v>2722</v>
       </c>
       <c r="E765" s="1" t="s">
         <v>1118</v>
@@ -21842,7 +21865,7 @@
         <v>1219</v>
       </c>
       <c r="D766" s="2" t="s">
-        <v>2724</v>
+        <v>2723</v>
       </c>
       <c r="E766" s="1" t="s">
         <v>1118</v>
@@ -21859,7 +21882,7 @@
         <v>1221</v>
       </c>
       <c r="D767" s="2" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="E767" s="1" t="s">
         <v>1118</v>
@@ -21876,7 +21899,7 @@
         <v>1223</v>
       </c>
       <c r="D768" s="2" t="s">
-        <v>2726</v>
+        <v>2725</v>
       </c>
       <c r="E768" s="1" t="s">
         <v>1118</v>
@@ -21893,7 +21916,7 @@
         <v>1225</v>
       </c>
       <c r="D769" s="2" t="s">
-        <v>2727</v>
+        <v>2726</v>
       </c>
       <c r="E769" s="1" t="s">
         <v>1118</v>
@@ -21910,7 +21933,7 @@
         <v>1227</v>
       </c>
       <c r="D770" s="2" t="s">
-        <v>2728</v>
+        <v>2727</v>
       </c>
       <c r="E770" s="1" t="s">
         <v>1118</v>
@@ -21927,7 +21950,7 @@
         <v>1229</v>
       </c>
       <c r="D771" s="2" t="s">
-        <v>2729</v>
+        <v>2728</v>
       </c>
       <c r="E771" s="1" t="s">
         <v>1118</v>
@@ -21944,7 +21967,7 @@
         <v>1231</v>
       </c>
       <c r="D772" s="2" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
       <c r="E772" s="1" t="s">
         <v>1118</v>
@@ -21961,7 +21984,7 @@
         <v>1233</v>
       </c>
       <c r="D773" s="2" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="E773" s="1" t="s">
         <v>1118</v>
@@ -21978,7 +22001,7 @@
         <v>1235</v>
       </c>
       <c r="D774" s="2" t="s">
-        <v>2732</v>
+        <v>2731</v>
       </c>
       <c r="E774" s="1" t="s">
         <v>1118</v>
@@ -21995,7 +22018,7 @@
         <v>1237</v>
       </c>
       <c r="D775" s="2" t="s">
-        <v>2733</v>
+        <v>2732</v>
       </c>
       <c r="E775" s="1" t="s">
         <v>1118</v>
@@ -22012,7 +22035,7 @@
         <v>1239</v>
       </c>
       <c r="D776" s="2" t="s">
-        <v>2734</v>
+        <v>2733</v>
       </c>
       <c r="E776" s="1" t="s">
         <v>1118</v>
@@ -22029,7 +22052,7 @@
         <v>1241</v>
       </c>
       <c r="D777" s="2" t="s">
-        <v>2735</v>
+        <v>2734</v>
       </c>
       <c r="E777" s="1" t="s">
         <v>1118</v>
@@ -22046,7 +22069,7 @@
         <v>1243</v>
       </c>
       <c r="D778" s="2" t="s">
-        <v>2736</v>
+        <v>2735</v>
       </c>
       <c r="E778" s="1" t="s">
         <v>1118</v>
@@ -22063,7 +22086,7 @@
         <v>1245</v>
       </c>
       <c r="D779" s="2" t="s">
-        <v>2737</v>
+        <v>2736</v>
       </c>
       <c r="E779" s="1" t="s">
         <v>1118</v>
@@ -22080,7 +22103,7 @@
         <v>1247</v>
       </c>
       <c r="D780" s="2" t="s">
-        <v>2738</v>
+        <v>2737</v>
       </c>
       <c r="E780" s="1" t="s">
         <v>1118</v>
@@ -22097,7 +22120,7 @@
         <v>1249</v>
       </c>
       <c r="D781" s="2" t="s">
-        <v>2739</v>
+        <v>2738</v>
       </c>
       <c r="E781" s="1" t="s">
         <v>1118</v>
@@ -22114,7 +22137,7 @@
         <v>1251</v>
       </c>
       <c r="D782" s="2" t="s">
-        <v>2740</v>
+        <v>2739</v>
       </c>
       <c r="E782" s="1" t="s">
         <v>1118</v>
@@ -22131,7 +22154,7 @@
         <v>1253</v>
       </c>
       <c r="D783" s="2" t="s">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="E783" s="1" t="s">
         <v>1118</v>
@@ -22148,7 +22171,7 @@
         <v>1255</v>
       </c>
       <c r="D784" s="2" t="s">
-        <v>2742</v>
+        <v>2741</v>
       </c>
       <c r="E784" s="1" t="s">
         <v>1118</v>
@@ -22165,7 +22188,7 @@
         <v>1257</v>
       </c>
       <c r="D785" s="2" t="s">
-        <v>2743</v>
+        <v>2742</v>
       </c>
       <c r="E785" s="1" t="s">
         <v>1118</v>
@@ -22182,7 +22205,7 @@
         <v>1259</v>
       </c>
       <c r="D786" s="2" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
       <c r="E786" s="1" t="s">
         <v>1118</v>
@@ -22199,7 +22222,7 @@
         <v>1261</v>
       </c>
       <c r="D787" s="2" t="s">
-        <v>2745</v>
+        <v>2744</v>
       </c>
       <c r="E787" s="1" t="s">
         <v>1118</v>
@@ -22216,7 +22239,7 @@
         <v>1263</v>
       </c>
       <c r="D788" s="2" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="E788" s="1" t="s">
         <v>1118</v>
@@ -22233,7 +22256,7 @@
         <v>1265</v>
       </c>
       <c r="D789" s="2" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="E789" s="1" t="s">
         <v>1118</v>
@@ -22250,7 +22273,7 @@
         <v>1267</v>
       </c>
       <c r="D790" s="2" t="s">
-        <v>2748</v>
+        <v>2747</v>
       </c>
       <c r="E790" s="1" t="s">
         <v>1118</v>
@@ -22267,7 +22290,7 @@
         <v>1269</v>
       </c>
       <c r="D791" s="2" t="s">
-        <v>2749</v>
+        <v>2748</v>
       </c>
       <c r="E791" s="1" t="s">
         <v>1118</v>
@@ -22284,7 +22307,7 @@
         <v>1271</v>
       </c>
       <c r="D792" s="2" t="s">
-        <v>2750</v>
+        <v>2749</v>
       </c>
       <c r="E792" s="1" t="s">
         <v>1118</v>
@@ -22301,7 +22324,7 @@
         <v>1273</v>
       </c>
       <c r="D793" s="2" t="s">
-        <v>2751</v>
+        <v>2750</v>
       </c>
       <c r="E793" s="1" t="s">
         <v>1118</v>
@@ -22318,7 +22341,7 @@
         <v>1275</v>
       </c>
       <c r="D794" s="2" t="s">
-        <v>2752</v>
+        <v>2751</v>
       </c>
       <c r="E794" s="1" t="s">
         <v>1118</v>
@@ -22335,7 +22358,7 @@
         <v>1277</v>
       </c>
       <c r="D795" s="2" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="E795" s="1" t="s">
         <v>1118</v>
@@ -22352,7 +22375,7 @@
         <v>1279</v>
       </c>
       <c r="D796" s="2" t="s">
-        <v>2754</v>
+        <v>2753</v>
       </c>
       <c r="E796" s="1" t="s">
         <v>1118</v>
@@ -22369,7 +22392,7 @@
         <v>1281</v>
       </c>
       <c r="D797" s="2" t="s">
-        <v>2755</v>
+        <v>2754</v>
       </c>
       <c r="E797" s="1" t="s">
         <v>1118</v>
@@ -22386,7 +22409,7 @@
         <v>1283</v>
       </c>
       <c r="D798" s="2" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="E798" s="1" t="s">
         <v>1118</v>
@@ -22403,7 +22426,7 @@
         <v>1285</v>
       </c>
       <c r="D799" s="2" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="E799" s="1" t="s">
         <v>1118</v>
@@ -22420,7 +22443,7 @@
         <v>1287</v>
       </c>
       <c r="D800" s="2" t="s">
-        <v>2758</v>
+        <v>2757</v>
       </c>
       <c r="E800" s="1" t="s">
         <v>1118</v>
@@ -22437,7 +22460,7 @@
         <v>1289</v>
       </c>
       <c r="D801" s="2" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
       <c r="E801" s="1" t="s">
         <v>1118</v>
@@ -22454,7 +22477,7 @@
         <v>1291</v>
       </c>
       <c r="D802" s="2" t="s">
-        <v>2760</v>
+        <v>2759</v>
       </c>
       <c r="E802" s="1" t="s">
         <v>1118</v>
@@ -22471,7 +22494,7 @@
         <v>1293</v>
       </c>
       <c r="D803" s="2" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="E803" s="1" t="s">
         <v>1118</v>
@@ -22488,7 +22511,7 @@
         <v>1295</v>
       </c>
       <c r="D804" s="2" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="E804" s="1" t="s">
         <v>1118</v>
@@ -22505,7 +22528,7 @@
         <v>1297</v>
       </c>
       <c r="D805" s="2" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="E805" s="1" t="s">
         <v>1118</v>
@@ -22522,7 +22545,7 @@
         <v>1299</v>
       </c>
       <c r="D806" s="2" t="s">
-        <v>2764</v>
+        <v>2763</v>
       </c>
       <c r="E806" s="1" t="s">
         <v>1118</v>
@@ -22539,7 +22562,7 @@
         <v>1301</v>
       </c>
       <c r="D807" s="2" t="s">
-        <v>2765</v>
+        <v>2764</v>
       </c>
       <c r="E807" s="1" t="s">
         <v>1118</v>
@@ -22556,7 +22579,7 @@
         <v>1303</v>
       </c>
       <c r="D808" s="2" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="E808" s="1" t="s">
         <v>1118</v>
@@ -22573,7 +22596,7 @@
         <v>1305</v>
       </c>
       <c r="D809" s="2" t="s">
-        <v>2767</v>
+        <v>2766</v>
       </c>
       <c r="E809" s="1" t="s">
         <v>1118</v>
@@ -22590,7 +22613,7 @@
         <v>1307</v>
       </c>
       <c r="D810" s="2" t="s">
-        <v>2768</v>
+        <v>2767</v>
       </c>
       <c r="E810" s="1" t="s">
         <v>1118</v>
@@ -22607,7 +22630,7 @@
         <v>1309</v>
       </c>
       <c r="D811" s="2" t="s">
-        <v>2769</v>
+        <v>2768</v>
       </c>
       <c r="E811" s="1" t="s">
         <v>1118</v>
@@ -22624,7 +22647,7 @@
         <v>1311</v>
       </c>
       <c r="D812" s="2" t="s">
-        <v>2770</v>
+        <v>2769</v>
       </c>
       <c r="E812" s="1" t="s">
         <v>1118</v>
@@ -22641,7 +22664,7 @@
         <v>1313</v>
       </c>
       <c r="D813" s="2" t="s">
-        <v>2771</v>
+        <v>2770</v>
       </c>
       <c r="E813" s="1" t="s">
         <v>1118</v>
@@ -22658,7 +22681,7 @@
         <v>1315</v>
       </c>
       <c r="D814" s="2" t="s">
-        <v>2772</v>
+        <v>2771</v>
       </c>
       <c r="E814" s="1" t="s">
         <v>1118</v>
@@ -22675,7 +22698,7 @@
         <v>1317</v>
       </c>
       <c r="D815" s="2" t="s">
-        <v>2773</v>
+        <v>2772</v>
       </c>
       <c r="E815" s="1" t="s">
         <v>1118</v>
@@ -22692,7 +22715,7 @@
         <v>1319</v>
       </c>
       <c r="D816" s="2" t="s">
-        <v>2774</v>
+        <v>2773</v>
       </c>
       <c r="E816" s="1" t="s">
         <v>1118</v>
@@ -22709,7 +22732,7 @@
         <v>1321</v>
       </c>
       <c r="D817" s="2" t="s">
-        <v>2775</v>
+        <v>2774</v>
       </c>
       <c r="E817" s="1" t="s">
         <v>1118</v>
@@ -22726,7 +22749,7 @@
         <v>1323</v>
       </c>
       <c r="D818" s="2" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
       <c r="E818" s="1" t="s">
         <v>1118</v>
@@ -22743,7 +22766,7 @@
         <v>1325</v>
       </c>
       <c r="D819" s="2" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
       <c r="E819" s="1" t="s">
         <v>1118</v>
@@ -22760,7 +22783,7 @@
         <v>1327</v>
       </c>
       <c r="D820" s="2" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="E820" s="1" t="s">
         <v>1118</v>
@@ -22777,7 +22800,7 @@
         <v>1329</v>
       </c>
       <c r="D821" s="2" t="s">
-        <v>2779</v>
+        <v>2778</v>
       </c>
       <c r="E821" s="1" t="s">
         <v>1118</v>
@@ -22794,7 +22817,7 @@
         <v>1331</v>
       </c>
       <c r="D822" s="2" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="E822" s="1" t="s">
         <v>1118</v>
@@ -22811,7 +22834,7 @@
         <v>1333</v>
       </c>
       <c r="D823" s="2" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
       <c r="E823" s="1" t="s">
         <v>1118</v>
@@ -22828,7 +22851,7 @@
         <v>1335</v>
       </c>
       <c r="D824" s="2" t="s">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="E824" s="1" t="s">
         <v>1118</v>
@@ -22845,7 +22868,7 @@
         <v>1337</v>
       </c>
       <c r="D825" s="2" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
       <c r="E825" s="1" t="s">
         <v>1118</v>
@@ -22862,7 +22885,7 @@
         <v>1339</v>
       </c>
       <c r="D826" s="2" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="E826" s="1" t="s">
         <v>1118</v>
@@ -22879,7 +22902,7 @@
         <v>1341</v>
       </c>
       <c r="D827" s="2" t="s">
-        <v>2785</v>
+        <v>2784</v>
       </c>
       <c r="E827" s="1" t="s">
         <v>1118</v>
@@ -22896,7 +22919,7 @@
         <v>1343</v>
       </c>
       <c r="D828" s="2" t="s">
-        <v>2786</v>
+        <v>2785</v>
       </c>
       <c r="E828" s="1" t="s">
         <v>1118</v>
@@ -22913,7 +22936,7 @@
         <v>1345</v>
       </c>
       <c r="D829" s="2" t="s">
-        <v>2787</v>
+        <v>2786</v>
       </c>
       <c r="E829" s="1" t="s">
         <v>1118</v>
@@ -22930,7 +22953,7 @@
         <v>1347</v>
       </c>
       <c r="D830" s="2" t="s">
-        <v>2788</v>
+        <v>2787</v>
       </c>
       <c r="E830" s="1" t="s">
         <v>1118</v>
@@ -22947,7 +22970,7 @@
         <v>1349</v>
       </c>
       <c r="D831" s="2" t="s">
-        <v>2789</v>
+        <v>2788</v>
       </c>
       <c r="E831" s="1" t="s">
         <v>1118</v>
@@ -22964,7 +22987,7 @@
         <v>1351</v>
       </c>
       <c r="D832" s="2" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
       <c r="E832" s="1" t="s">
         <v>1118</v>
@@ -22981,7 +23004,7 @@
         <v>1353</v>
       </c>
       <c r="D833" s="2" t="s">
-        <v>2791</v>
+        <v>2790</v>
       </c>
       <c r="E833" s="1" t="s">
         <v>1118</v>
@@ -22998,7 +23021,7 @@
         <v>1355</v>
       </c>
       <c r="D834" s="2" t="s">
-        <v>2792</v>
+        <v>2791</v>
       </c>
       <c r="E834" s="1" t="s">
         <v>1118</v>
@@ -23015,7 +23038,7 @@
         <v>1357</v>
       </c>
       <c r="D835" s="2" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
       <c r="E835" s="1" t="s">
         <v>1118</v>
@@ -23032,7 +23055,7 @@
         <v>1359</v>
       </c>
       <c r="D836" s="2" t="s">
-        <v>2794</v>
+        <v>2793</v>
       </c>
       <c r="E836" s="1" t="s">
         <v>1118</v>
@@ -23049,7 +23072,7 @@
         <v>1361</v>
       </c>
       <c r="D837" s="2" t="s">
-        <v>2795</v>
+        <v>2794</v>
       </c>
       <c r="E837" s="1" t="s">
         <v>1118</v>
@@ -23066,7 +23089,7 @@
         <v>1363</v>
       </c>
       <c r="D838" s="2" t="s">
-        <v>2796</v>
+        <v>2795</v>
       </c>
       <c r="E838" s="1" t="s">
         <v>1118</v>
@@ -23083,7 +23106,7 @@
         <v>1365</v>
       </c>
       <c r="D839" s="2" t="s">
-        <v>2797</v>
+        <v>2796</v>
       </c>
       <c r="E839" s="1" t="s">
         <v>1118</v>
@@ -23100,7 +23123,7 @@
         <v>1367</v>
       </c>
       <c r="D840" s="2" t="s">
-        <v>2798</v>
+        <v>2797</v>
       </c>
       <c r="E840" s="1" t="s">
         <v>1118</v>
@@ -23117,7 +23140,7 @@
         <v>1369</v>
       </c>
       <c r="D841" s="2" t="s">
-        <v>2799</v>
+        <v>2798</v>
       </c>
       <c r="E841" s="1" t="s">
         <v>1118</v>
@@ -23134,7 +23157,7 @@
         <v>1371</v>
       </c>
       <c r="D842" s="2" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
       <c r="E842" s="1" t="s">
         <v>1118</v>
@@ -23698,7 +23721,7 @@
         <v>1439</v>
       </c>
       <c r="E875" s="5" t="s">
-        <v>2664</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="876" spans="1:5" x14ac:dyDescent="0.2">
@@ -27387,7 +27410,7 @@
         <v>1873</v>
       </c>
       <c r="E1092" s="5" t="s">
-        <v>2663</v>
+        <v>2662</v>
       </c>
     </row>
     <row r="1093" spans="1:5" x14ac:dyDescent="0.2">
@@ -32096,7 +32119,7 @@
         <v>2404</v>
       </c>
       <c r="E1369" s="5" t="s">
-        <v>2661</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="1370" spans="1:5" x14ac:dyDescent="0.2">
@@ -33486,8 +33509,8 @@
       <c r="C1451" s="2" t="s">
         <v>2552</v>
       </c>
-      <c r="D1451" s="2" t="s">
-        <v>2553</v>
+      <c r="D1451" s="6" t="s">
+        <v>2807</v>
       </c>
       <c r="E1451" s="1" t="s">
         <v>1090</v>
@@ -33501,10 +33524,10 @@
         <v>1400160</v>
       </c>
       <c r="C1452" s="2" t="s">
+        <v>2553</v>
+      </c>
+      <c r="D1452" s="2" t="s">
         <v>2554</v>
-      </c>
-      <c r="D1452" s="2" t="s">
-        <v>2555</v>
       </c>
       <c r="E1452" s="1" t="s">
         <v>1090</v>
@@ -33518,10 +33541,10 @@
         <v>1400170</v>
       </c>
       <c r="C1453" s="2" t="s">
+        <v>2555</v>
+      </c>
+      <c r="D1453" s="2" t="s">
         <v>2556</v>
-      </c>
-      <c r="D1453" s="2" t="s">
-        <v>2557</v>
       </c>
       <c r="E1453" s="1" t="s">
         <v>1090</v>
@@ -33603,10 +33626,10 @@
         <v>1400220</v>
       </c>
       <c r="C1458" s="2" t="s">
+        <v>2557</v>
+      </c>
+      <c r="D1458" s="2" t="s">
         <v>2558</v>
-      </c>
-      <c r="D1458" s="2" t="s">
-        <v>2559</v>
       </c>
       <c r="E1458" s="1" t="s">
         <v>2490</v>
@@ -33620,10 +33643,10 @@
         <v>1400230</v>
       </c>
       <c r="C1459" s="2" t="s">
+        <v>2559</v>
+      </c>
+      <c r="D1459" s="2" t="s">
         <v>2560</v>
-      </c>
-      <c r="D1459" s="2" t="s">
-        <v>2561</v>
       </c>
       <c r="E1459" s="1" t="s">
         <v>2490</v>
@@ -33637,10 +33660,10 @@
         <v>1400240</v>
       </c>
       <c r="C1460" s="2" t="s">
+        <v>2561</v>
+      </c>
+      <c r="D1460" s="2" t="s">
         <v>2562</v>
-      </c>
-      <c r="D1460" s="2" t="s">
-        <v>2563</v>
       </c>
       <c r="E1460" s="1" t="s">
         <v>2490</v>
@@ -33654,10 +33677,10 @@
         <v>1400250</v>
       </c>
       <c r="C1461" s="2" t="s">
+        <v>2563</v>
+      </c>
+      <c r="D1461" s="2" t="s">
         <v>2564</v>
-      </c>
-      <c r="D1461" s="2" t="s">
-        <v>2565</v>
       </c>
       <c r="E1461" s="1" t="s">
         <v>2490</v>
@@ -33671,10 +33694,10 @@
         <v>1400260</v>
       </c>
       <c r="C1462" s="2" t="s">
+        <v>2565</v>
+      </c>
+      <c r="D1462" s="2" t="s">
         <v>2566</v>
-      </c>
-      <c r="D1462" s="2" t="s">
-        <v>2567</v>
       </c>
       <c r="E1462" s="1" t="s">
         <v>2490</v>
@@ -33722,13 +33745,13 @@
         <v>1400290</v>
       </c>
       <c r="C1465" s="2" t="s">
-        <v>2568</v>
+        <v>2567</v>
       </c>
       <c r="D1465" s="2" t="s">
         <v>2538</v>
       </c>
       <c r="E1465" s="5" t="s">
-        <v>2666</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="1466" spans="1:5" x14ac:dyDescent="0.2">
@@ -33739,10 +33762,10 @@
         <v>1400300</v>
       </c>
       <c r="C1466" s="2" t="s">
+        <v>2568</v>
+      </c>
+      <c r="D1466" s="2" t="s">
         <v>2569</v>
-      </c>
-      <c r="D1466" s="2" t="s">
-        <v>2570</v>
       </c>
       <c r="E1466" s="1" t="s">
         <v>2490</v>
@@ -33756,10 +33779,10 @@
         <v>1400310</v>
       </c>
       <c r="C1467" s="2" t="s">
+        <v>2570</v>
+      </c>
+      <c r="D1467" s="2" t="s">
         <v>2571</v>
-      </c>
-      <c r="D1467" s="2" t="s">
-        <v>2572</v>
       </c>
       <c r="E1467" s="1" t="s">
         <v>2490</v>
@@ -33773,10 +33796,10 @@
         <v>1400320</v>
       </c>
       <c r="C1468" s="3" t="s">
+        <v>2572</v>
+      </c>
+      <c r="D1468" s="3" t="s">
         <v>2573</v>
-      </c>
-      <c r="D1468" s="3" t="s">
-        <v>2574</v>
       </c>
       <c r="E1468" s="4" t="s">
         <v>2541</v>
@@ -33790,10 +33813,10 @@
         <v>1400330</v>
       </c>
       <c r="C1469" s="2" t="s">
+        <v>2574</v>
+      </c>
+      <c r="D1469" s="2" t="s">
         <v>2575</v>
-      </c>
-      <c r="D1469" s="2" t="s">
-        <v>2576</v>
       </c>
       <c r="E1469" s="1" t="s">
         <v>2490</v>
@@ -33824,10 +33847,10 @@
         <v>1400350</v>
       </c>
       <c r="C1471" s="2" t="s">
+        <v>2576</v>
+      </c>
+      <c r="D1471" s="2" t="s">
         <v>2577</v>
-      </c>
-      <c r="D1471" s="2" t="s">
-        <v>2578</v>
       </c>
       <c r="E1471" s="1" t="s">
         <v>2490</v>
@@ -33841,10 +33864,10 @@
         <v>1400360</v>
       </c>
       <c r="C1472" s="2" t="s">
+        <v>2578</v>
+      </c>
+      <c r="D1472" s="2" t="s">
         <v>2579</v>
-      </c>
-      <c r="D1472" s="2" t="s">
-        <v>2580</v>
       </c>
       <c r="E1472" s="1" t="s">
         <v>2490</v>
@@ -33858,10 +33881,10 @@
         <v>1400370</v>
       </c>
       <c r="C1473" s="2" t="s">
+        <v>2580</v>
+      </c>
+      <c r="D1473" s="2" t="s">
         <v>2581</v>
-      </c>
-      <c r="D1473" s="2" t="s">
-        <v>2582</v>
       </c>
       <c r="E1473" s="1" t="s">
         <v>2490</v>
@@ -33875,10 +33898,10 @@
         <v>1400380</v>
       </c>
       <c r="C1474" s="2" t="s">
+        <v>2582</v>
+      </c>
+      <c r="D1474" s="2" t="s">
         <v>2583</v>
-      </c>
-      <c r="D1474" s="2" t="s">
-        <v>2584</v>
       </c>
       <c r="E1474" s="1" t="s">
         <v>2490</v>
@@ -33892,10 +33915,10 @@
         <v>1400390</v>
       </c>
       <c r="C1475" s="2" t="s">
+        <v>2584</v>
+      </c>
+      <c r="D1475" s="2" t="s">
         <v>2585</v>
-      </c>
-      <c r="D1475" s="2" t="s">
-        <v>2586</v>
       </c>
       <c r="E1475" s="1" t="s">
         <v>2490</v>
@@ -33909,10 +33932,10 @@
         <v>1400400</v>
       </c>
       <c r="C1476" s="2" t="s">
+        <v>2586</v>
+      </c>
+      <c r="D1476" s="2" t="s">
         <v>2587</v>
-      </c>
-      <c r="D1476" s="2" t="s">
-        <v>2588</v>
       </c>
       <c r="E1476" s="1" t="s">
         <v>2490</v>
@@ -33926,10 +33949,10 @@
         <v>1400410</v>
       </c>
       <c r="C1477" s="2" t="s">
+        <v>2588</v>
+      </c>
+      <c r="D1477" s="2" t="s">
         <v>2589</v>
-      </c>
-      <c r="D1477" s="2" t="s">
-        <v>2590</v>
       </c>
       <c r="E1477" s="1" t="s">
         <v>2490</v>
@@ -33943,10 +33966,10 @@
         <v>1400420</v>
       </c>
       <c r="C1478" s="2" t="s">
+        <v>2590</v>
+      </c>
+      <c r="D1478" s="2" t="s">
         <v>2591</v>
-      </c>
-      <c r="D1478" s="2" t="s">
-        <v>2592</v>
       </c>
       <c r="E1478" s="1" t="s">
         <v>2490</v>
@@ -33960,10 +33983,10 @@
         <v>1400430</v>
       </c>
       <c r="C1479" s="2" t="s">
+        <v>2592</v>
+      </c>
+      <c r="D1479" s="2" t="s">
         <v>2593</v>
-      </c>
-      <c r="D1479" s="2" t="s">
-        <v>2594</v>
       </c>
       <c r="E1479" s="1" t="s">
         <v>2320</v>
@@ -33977,10 +34000,10 @@
         <v>1400440</v>
       </c>
       <c r="C1480" s="2" t="s">
+        <v>2594</v>
+      </c>
+      <c r="D1480" s="2" t="s">
         <v>2595</v>
-      </c>
-      <c r="D1480" s="2" t="s">
-        <v>2596</v>
       </c>
       <c r="E1480" s="1" t="s">
         <v>2320</v>
@@ -33994,10 +34017,10 @@
         <v>1400441</v>
       </c>
       <c r="C1481" s="2" t="s">
-        <v>2597</v>
+        <v>2596</v>
       </c>
       <c r="D1481" s="2" t="s">
-        <v>2597</v>
+        <v>2596</v>
       </c>
       <c r="E1481" s="1" t="s">
         <v>2490</v>
@@ -34011,13 +34034,13 @@
         <v>1400442</v>
       </c>
       <c r="C1482" s="3" t="s">
-        <v>2598</v>
+        <v>2597</v>
       </c>
       <c r="D1482" s="3" t="s">
-        <v>2598</v>
+        <v>2597</v>
       </c>
       <c r="E1482" s="5" t="s">
-        <v>2665</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="1483" spans="1:5" x14ac:dyDescent="0.2">
@@ -34028,10 +34051,10 @@
         <v>1400500</v>
       </c>
       <c r="C1483" s="3" t="s">
-        <v>2599</v>
+        <v>2598</v>
       </c>
       <c r="D1483" s="6" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="E1483" s="4" t="s">
         <v>2490</v>
@@ -34045,10 +34068,10 @@
         <v>1400600</v>
       </c>
       <c r="C1484" s="3" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="D1484" s="3" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="E1484" s="4" t="s">
         <v>2490</v>
@@ -34062,10 +34085,10 @@
         <v>1400443</v>
       </c>
       <c r="C1485" s="2" t="s">
-        <v>2601</v>
+        <v>2600</v>
       </c>
       <c r="D1485" s="2" t="s">
-        <v>2601</v>
+        <v>2600</v>
       </c>
       <c r="E1485" s="4" t="s">
         <v>2490</v>
@@ -34079,10 +34102,10 @@
         <v>1400444</v>
       </c>
       <c r="C1486" s="2" t="s">
+        <v>2601</v>
+      </c>
+      <c r="D1486" s="2" t="s">
         <v>2602</v>
-      </c>
-      <c r="D1486" s="2" t="s">
-        <v>2603</v>
       </c>
       <c r="E1486" s="1" t="s">
         <v>2490</v>
@@ -34096,10 +34119,10 @@
         <v>1400445</v>
       </c>
       <c r="C1487" s="2" t="s">
-        <v>2604</v>
+        <v>2603</v>
       </c>
       <c r="D1487" s="2" t="s">
-        <v>2604</v>
+        <v>2603</v>
       </c>
       <c r="E1487" s="1" t="s">
         <v>1090</v>
@@ -34113,10 +34136,10 @@
         <v>1400446</v>
       </c>
       <c r="C1488" s="2" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
       <c r="D1488" s="2" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
       <c r="E1488" s="1" t="s">
         <v>2425</v>
@@ -34130,10 +34153,10 @@
         <v>1400447</v>
       </c>
       <c r="C1489" s="2" t="s">
-        <v>2606</v>
+        <v>2605</v>
       </c>
       <c r="D1489" s="2" t="s">
-        <v>2606</v>
+        <v>2605</v>
       </c>
       <c r="E1489" s="1" t="s">
         <v>2425</v>
@@ -34147,10 +34170,10 @@
         <v>1400448</v>
       </c>
       <c r="C1490" s="2" t="s">
+        <v>2606</v>
+      </c>
+      <c r="D1490" s="2" t="s">
         <v>2607</v>
-      </c>
-      <c r="D1490" s="2" t="s">
-        <v>2608</v>
       </c>
       <c r="E1490" s="1" t="s">
         <v>2425</v>
@@ -34164,10 +34187,10 @@
         <v>1400449</v>
       </c>
       <c r="C1491" s="2" t="s">
+        <v>2608</v>
+      </c>
+      <c r="D1491" s="2" t="s">
         <v>2609</v>
-      </c>
-      <c r="D1491" s="2" t="s">
-        <v>2610</v>
       </c>
       <c r="E1491" s="1" t="s">
         <v>2425</v>
@@ -34181,10 +34204,10 @@
         <v>1400450</v>
       </c>
       <c r="C1492" s="2" t="s">
+        <v>2610</v>
+      </c>
+      <c r="D1492" s="2" t="s">
         <v>2611</v>
-      </c>
-      <c r="D1492" s="2" t="s">
-        <v>2612</v>
       </c>
       <c r="E1492" s="1" t="s">
         <v>2425</v>
@@ -34198,10 +34221,10 @@
         <v>1400451</v>
       </c>
       <c r="C1493" s="2" t="s">
+        <v>2612</v>
+      </c>
+      <c r="D1493" s="2" t="s">
         <v>2613</v>
-      </c>
-      <c r="D1493" s="2" t="s">
-        <v>2614</v>
       </c>
       <c r="E1493" s="1" t="s">
         <v>2425</v>
@@ -34215,10 +34238,10 @@
         <v>1400452</v>
       </c>
       <c r="C1494" s="2" t="s">
+        <v>2614</v>
+      </c>
+      <c r="D1494" s="2" t="s">
         <v>2615</v>
-      </c>
-      <c r="D1494" s="2" t="s">
-        <v>2616</v>
       </c>
       <c r="E1494" s="1" t="s">
         <v>2425</v>
@@ -34232,10 +34255,10 @@
         <v>1400453</v>
       </c>
       <c r="C1495" s="2" t="s">
+        <v>2616</v>
+      </c>
+      <c r="D1495" s="2" t="s">
         <v>2617</v>
-      </c>
-      <c r="D1495" s="2" t="s">
-        <v>2618</v>
       </c>
       <c r="E1495" s="1" t="s">
         <v>2425</v>
@@ -34249,10 +34272,10 @@
         <v>1400454</v>
       </c>
       <c r="C1496" s="2" t="s">
+        <v>2618</v>
+      </c>
+      <c r="D1496" s="2" t="s">
         <v>2619</v>
-      </c>
-      <c r="D1496" s="2" t="s">
-        <v>2620</v>
       </c>
       <c r="E1496" s="1" t="s">
         <v>2425</v>
@@ -34266,10 +34289,10 @@
         <v>1400455</v>
       </c>
       <c r="C1497" s="2" t="s">
+        <v>2620</v>
+      </c>
+      <c r="D1497" s="2" t="s">
         <v>2621</v>
-      </c>
-      <c r="D1497" s="2" t="s">
-        <v>2622</v>
       </c>
       <c r="E1497" s="1" t="s">
         <v>2425</v>
@@ -34283,10 +34306,10 @@
         <v>1400456</v>
       </c>
       <c r="C1498" s="2" t="s">
+        <v>2622</v>
+      </c>
+      <c r="D1498" s="2" t="s">
         <v>2623</v>
-      </c>
-      <c r="D1498" s="2" t="s">
-        <v>2624</v>
       </c>
       <c r="E1498" s="1" t="s">
         <v>2425</v>
@@ -34300,13 +34323,13 @@
         <v>1400457</v>
       </c>
       <c r="C1499" s="2" t="s">
+        <v>2624</v>
+      </c>
+      <c r="D1499" s="2" t="s">
         <v>2625</v>
       </c>
-      <c r="D1499" s="2" t="s">
-        <v>2626</v>
-      </c>
       <c r="E1499" s="5" t="s">
-        <v>2662</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="1500" spans="1:5" x14ac:dyDescent="0.2">
@@ -34317,13 +34340,13 @@
         <v>1400460</v>
       </c>
       <c r="C1500" s="2" t="s">
+        <v>2626</v>
+      </c>
+      <c r="D1500" s="2" t="s">
         <v>2627</v>
       </c>
-      <c r="D1500" s="2" t="s">
-        <v>2628</v>
-      </c>
       <c r="E1500" s="5" t="s">
-        <v>2645</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="1501" spans="1:5" x14ac:dyDescent="0.2">
@@ -34334,10 +34357,10 @@
         <v>1400461</v>
       </c>
       <c r="C1501" s="2" t="s">
+        <v>2628</v>
+      </c>
+      <c r="D1501" s="2" t="s">
         <v>2629</v>
-      </c>
-      <c r="D1501" s="2" t="s">
-        <v>2630</v>
       </c>
       <c r="E1501" s="1" t="s">
         <v>561</v>
@@ -34351,10 +34374,10 @@
         <v>1400462</v>
       </c>
       <c r="C1502" s="2" t="s">
+        <v>2630</v>
+      </c>
+      <c r="D1502" s="2" t="s">
         <v>2631</v>
-      </c>
-      <c r="D1502" s="2" t="s">
-        <v>2632</v>
       </c>
       <c r="E1502" s="1" t="s">
         <v>568</v>
@@ -34368,10 +34391,10 @@
         <v>1400463</v>
       </c>
       <c r="C1503" s="2" t="s">
+        <v>2632</v>
+      </c>
+      <c r="D1503" s="2" t="s">
         <v>2633</v>
-      </c>
-      <c r="D1503" s="2" t="s">
-        <v>2634</v>
       </c>
       <c r="E1503" s="1" t="s">
         <v>575</v>
@@ -34385,10 +34408,10 @@
         <v>1400464</v>
       </c>
       <c r="C1504" s="2" t="s">
+        <v>2634</v>
+      </c>
+      <c r="D1504" s="2" t="s">
         <v>2635</v>
-      </c>
-      <c r="D1504" s="2" t="s">
-        <v>2636</v>
       </c>
       <c r="E1504" s="1" t="s">
         <v>582</v>
@@ -34402,10 +34425,10 @@
         <v>1400465</v>
       </c>
       <c r="C1505" s="2" t="s">
+        <v>2636</v>
+      </c>
+      <c r="D1505" s="2" t="s">
         <v>2637</v>
-      </c>
-      <c r="D1505" s="2" t="s">
-        <v>2638</v>
       </c>
       <c r="E1505" s="1" t="s">
         <v>589</v>
@@ -34419,10 +34442,10 @@
         <v>1400466</v>
       </c>
       <c r="C1506" s="2" t="s">
+        <v>2638</v>
+      </c>
+      <c r="D1506" s="2" t="s">
         <v>2639</v>
-      </c>
-      <c r="D1506" s="2" t="s">
-        <v>2640</v>
       </c>
       <c r="E1506" s="1" t="s">
         <v>596</v>
@@ -34436,10 +34459,10 @@
         <v>1400467</v>
       </c>
       <c r="C1507" s="2" t="s">
+        <v>2640</v>
+      </c>
+      <c r="D1507" s="2" t="s">
         <v>2641</v>
-      </c>
-      <c r="D1507" s="2" t="s">
-        <v>2642</v>
       </c>
       <c r="E1507" s="1" t="s">
         <v>603</v>
@@ -34453,13 +34476,13 @@
         <v>1400468</v>
       </c>
       <c r="C1508" s="2" t="s">
+        <v>2642</v>
+      </c>
+      <c r="D1508" s="2" t="s">
         <v>2643</v>
       </c>
-      <c r="D1508" s="2" t="s">
-        <v>2644</v>
-      </c>
       <c r="E1508" s="5" t="s">
-        <v>2646</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="1509" spans="1:5" x14ac:dyDescent="0.2">
@@ -34470,10 +34493,10 @@
         <v>1400469</v>
       </c>
       <c r="C1509" s="6" t="s">
-        <v>2647</v>
+        <v>2646</v>
       </c>
       <c r="D1509" s="6" t="s">
-        <v>2647</v>
+        <v>2646</v>
       </c>
       <c r="E1509" s="1" t="s">
         <v>2490</v>
@@ -34487,10 +34510,10 @@
         <v>1400470</v>
       </c>
       <c r="C1510" s="6" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
       <c r="D1510" s="6" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
       <c r="E1510" s="1" t="s">
         <v>2490</v>
@@ -34504,10 +34527,10 @@
         <v>1400471</v>
       </c>
       <c r="C1511" s="6" t="s">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="D1511" s="6" t="s">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="E1511" s="1" t="s">
         <v>2490</v>
@@ -34521,13 +34544,13 @@
         <v>1400472</v>
       </c>
       <c r="C1512" s="6" t="s">
+        <v>2649</v>
+      </c>
+      <c r="D1512" s="6" t="s">
+        <v>2649</v>
+      </c>
+      <c r="E1512" s="5" t="s">
         <v>2650</v>
-      </c>
-      <c r="D1512" s="6" t="s">
-        <v>2650</v>
-      </c>
-      <c r="E1512" s="5" t="s">
-        <v>2651</v>
       </c>
     </row>
     <row r="1513" spans="1:5" x14ac:dyDescent="0.2">
@@ -34538,10 +34561,10 @@
         <v>1400480</v>
       </c>
       <c r="C1513" s="6" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="D1513" s="6" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="E1513" s="1" t="s">
         <v>1375</v>
@@ -34555,13 +34578,13 @@
         <v>1400481</v>
       </c>
       <c r="C1514" s="6" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
       <c r="D1514" s="6" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
       <c r="E1514" s="5" t="s">
-        <v>2665</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="1515" spans="1:5" x14ac:dyDescent="0.2">
@@ -34572,10 +34595,10 @@
         <v>1400482</v>
       </c>
       <c r="C1515" s="6" t="s">
-        <v>2655</v>
+        <v>2654</v>
       </c>
       <c r="D1515" s="6" t="s">
-        <v>2655</v>
+        <v>2654</v>
       </c>
       <c r="E1515" s="1" t="s">
         <v>1375</v>
@@ -34589,10 +34612,10 @@
         <v>1400483</v>
       </c>
       <c r="C1516" s="6" t="s">
-        <v>2656</v>
+        <v>2655</v>
       </c>
       <c r="D1516" s="6" t="s">
-        <v>2656</v>
+        <v>2655</v>
       </c>
       <c r="E1516" s="1" t="s">
         <v>1375</v>
@@ -34606,10 +34629,10 @@
         <v>1400484</v>
       </c>
       <c r="C1517" s="6" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="D1517" s="6" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="E1517" s="1" t="s">
         <v>1375</v>
@@ -34623,10 +34646,10 @@
         <v>1400485</v>
       </c>
       <c r="C1518" s="6" t="s">
-        <v>2658</v>
+        <v>2657</v>
       </c>
       <c r="D1518" s="6" t="s">
-        <v>2658</v>
+        <v>2657</v>
       </c>
       <c r="E1518" s="1" t="s">
         <v>1375</v>
@@ -34640,10 +34663,10 @@
         <v>1400486</v>
       </c>
       <c r="C1519" s="6" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
       <c r="D1519" s="6" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
       <c r="E1519" s="1" t="s">
         <v>1375</v>
@@ -34657,10 +34680,10 @@
         <v>1400487</v>
       </c>
       <c r="C1520" s="6" t="s">
-        <v>2660</v>
+        <v>2659</v>
       </c>
       <c r="D1520" s="6" t="s">
-        <v>2660</v>
+        <v>2659</v>
       </c>
       <c r="E1520" s="1" t="s">
         <v>1375</v>
@@ -34674,10 +34697,10 @@
         <v>1400488</v>
       </c>
       <c r="C1521" s="6" t="s">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="D1521" s="6" t="s">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="E1521" s="1" t="s">
         <v>1090</v>
@@ -34691,10 +34714,10 @@
         <v>1400489</v>
       </c>
       <c r="C1522" s="6" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
       <c r="D1522" s="6" t="s">
-        <v>2801</v>
+        <v>2800</v>
       </c>
       <c r="E1522" s="1" t="s">
         <v>2490</v>
@@ -34708,10 +34731,10 @@
         <v>1400490</v>
       </c>
       <c r="C1523" s="6" t="s">
-        <v>2802</v>
+        <v>2801</v>
       </c>
       <c r="D1523" s="6" t="s">
-        <v>2802</v>
+        <v>2801</v>
       </c>
       <c r="E1523" s="1" t="s">
         <v>2490</v>
@@ -34725,13 +34748,81 @@
         <v>1400491</v>
       </c>
       <c r="C1524" s="6" t="s">
-        <v>2803</v>
+        <v>2802</v>
       </c>
       <c r="D1524" s="6" t="s">
-        <v>2803</v>
+        <v>2802</v>
       </c>
       <c r="E1524" s="1" t="s">
         <v>2490</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1525" s="8">
+        <v>17</v>
+      </c>
+      <c r="B1525" s="8">
+        <v>1400492</v>
+      </c>
+      <c r="C1525" s="7" t="s">
+        <v>2803</v>
+      </c>
+      <c r="D1525" s="7" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E1525" s="8" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1526" s="8">
+        <v>17</v>
+      </c>
+      <c r="B1526" s="8">
+        <v>1400493</v>
+      </c>
+      <c r="C1526" s="7" t="s">
+        <v>2804</v>
+      </c>
+      <c r="D1526" s="7" t="s">
+        <v>2804</v>
+      </c>
+      <c r="E1526" s="8" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1527" s="8">
+        <v>17</v>
+      </c>
+      <c r="B1527" s="8">
+        <v>1400494</v>
+      </c>
+      <c r="C1527" s="7" t="s">
+        <v>2805</v>
+      </c>
+      <c r="D1527" s="7" t="s">
+        <v>2805</v>
+      </c>
+      <c r="E1527" s="8" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1528" s="8">
+        <v>17</v>
+      </c>
+      <c r="B1528" s="8">
+        <v>1400495</v>
+      </c>
+      <c r="C1528" s="7" t="s">
+        <v>2806</v>
+      </c>
+      <c r="D1528" s="7" t="s">
+        <v>2806</v>
+      </c>
+      <c r="E1528" s="8" t="s">
+        <v>486</v>
       </c>
     </row>
   </sheetData>
